--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_3/epoch_150/per_file_predictions_epoch_150.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_3/epoch_150/per_file_predictions_epoch_150.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9629,0.0015,0.0230,0.0018</t>
-  </si>
-  <si>
-    <t>0.9531,0.0007,0.0022,0.0240</t>
-  </si>
-  <si>
-    <t>0.9723,0.0014,0.0051,0.0155</t>
-  </si>
-  <si>
-    <t>0.9590,0.0008,0.0009,0.0414</t>
-  </si>
-  <si>
-    <t>0.9010,0.0025,0.0029,0.0794</t>
-  </si>
-  <si>
-    <t>0.6025,0.0610,0.0058,0.0502</t>
-  </si>
-  <si>
-    <t>0.8315,0.0022,0.0050,0.2033</t>
-  </si>
-  <si>
-    <t>0.9612,0.0013,0.0004,0.0224</t>
-  </si>
-  <si>
-    <t>0.9377,0.0011,0.0003,0.0549</t>
-  </si>
-  <si>
-    <t>0.8992,0.0029,0.0042,0.1098</t>
-  </si>
-  <si>
-    <t>0.8777,0.0017,0.0040,0.1012</t>
-  </si>
-  <si>
-    <t>0.9651,0.0018,0.0022,0.0201</t>
-  </si>
-  <si>
-    <t>0.9871,0.0008,0.0058,0.0001</t>
-  </si>
-  <si>
-    <t>0.3929,0.0149,0.7781,0.0015</t>
-  </si>
-  <si>
-    <t>0.9262,0.0025,0.1165,0.0009</t>
-  </si>
-  <si>
-    <t>0.5543,0.0018,0.6863,0.0009</t>
-  </si>
-  <si>
-    <t>0.9521,0.0034,0.0316,0.0023</t>
-  </si>
-  <si>
-    <t>0.9188,0.0259,0.0241,0.0006</t>
-  </si>
-  <si>
-    <t>0.8791,0.0483,0.0339,0.0014</t>
-  </si>
-  <si>
-    <t>0.9888,0.0005,0.0019,0.0010</t>
-  </si>
-  <si>
-    <t>0.8040,0.1401,0.0266,0.0014</t>
-  </si>
-  <si>
-    <t>0.9245,0.0236,0.0303,0.0005</t>
-  </si>
-  <si>
-    <t>0.9547,0.0013,0.0636,0.0005</t>
-  </si>
-  <si>
-    <t>0.9896,0.0005,0.0089,0.0001</t>
-  </si>
-  <si>
-    <t>0.5361,0.0005,0.7306,0.0001</t>
-  </si>
-  <si>
-    <t>0.8940,0.0010,0.0708,0.0041</t>
-  </si>
-  <si>
-    <t>0.8595,0.0037,0.2365,0.0014</t>
-  </si>
-  <si>
-    <t>0.4535,0.0062,0.7671,0.0006</t>
-  </si>
-  <si>
-    <t>0.0265,0.0118,0.9757,0.0011</t>
-  </si>
-  <si>
-    <t>0.9724,0.0042,0.0113,0.0005</t>
-  </si>
-  <si>
-    <t>0.9648,0.0109,0.0141,0.0014</t>
-  </si>
-  <si>
-    <t>0.1437,0.0704,0.9281,0.0047</t>
-  </si>
-  <si>
-    <t>0.9299,0.0041,0.0871,0.0002</t>
-  </si>
-  <si>
-    <t>0.9815,0.0008,0.0019,0.0045</t>
-  </si>
-  <si>
-    <t>0.9778,0.0032,0.0036,0.0019</t>
-  </si>
-  <si>
-    <t>0.9267,0.0050,0.0284,0.0056</t>
-  </si>
-  <si>
-    <t>0.9033,0.0355,0.0377,0.0023</t>
-  </si>
-  <si>
-    <t>0.5046,0.0947,0.5079,0.0060</t>
-  </si>
-  <si>
-    <t>0.6388,0.0009,0.5513,0.0003</t>
-  </si>
-  <si>
-    <t>0.9089,0.0010,0.1628,0.0003</t>
-  </si>
-  <si>
-    <t>0.4982,0.0010,0.5202,0.0021</t>
-  </si>
-  <si>
-    <t>0.4120,0.0069,0.7518,0.0013</t>
-  </si>
-  <si>
-    <t>0.2809,0.6876,0.0608,0.0002</t>
-  </si>
-  <si>
-    <t>0.5480,0.0105,0.6407,0.0006</t>
-  </si>
-  <si>
-    <t>0.9262,0.0146,0.0302,0.0054</t>
-  </si>
-  <si>
-    <t>0.9374,0.0275,0.0060,0.0008</t>
-  </si>
-  <si>
-    <t>0.9631,0.0219,0.0026,0.0007</t>
-  </si>
-  <si>
-    <t>0.9429,0.0263,0.0061,0.0004</t>
-  </si>
-  <si>
-    <t>0.3046,0.0256,0.7552,0.0005</t>
-  </si>
-  <si>
-    <t>0.0025,0.0154,0.9949,0.0002</t>
-  </si>
-  <si>
-    <t>0.5100,0.0385,0.6558,0.0028</t>
-  </si>
-  <si>
-    <t>0.7617,0.0030,0.4526,0.0007</t>
-  </si>
-  <si>
-    <t>0.0170,0.0107,0.9892,0.0001</t>
-  </si>
-  <si>
-    <t>0.5587,0.0114,0.6560,0.0012</t>
-  </si>
-  <si>
-    <t>0.9313,0.0037,0.0018,0.0358</t>
-  </si>
-  <si>
-    <t>0.9005,0.0192,0.0234,0.0128</t>
-  </si>
-  <si>
-    <t>0.9237,0.0053,0.0021,0.0613</t>
-  </si>
-  <si>
-    <t>0.1325,0.1539,0.8600,0.0062</t>
-  </si>
-  <si>
-    <t>0.9461,0.0042,0.0032,0.0224</t>
-  </si>
-  <si>
-    <t>0.9708,0.0015,0.0009,0.0154</t>
-  </si>
-  <si>
-    <t>0.9393,0.0085,0.0060,0.0159</t>
-  </si>
-  <si>
-    <t>0.0266,0.6191,0.9556,0.0012</t>
-  </si>
-  <si>
-    <t>0.9217,0.0017,0.1252,0.0002</t>
-  </si>
-  <si>
-    <t>0.0953,0.0040,0.9266,0.0016</t>
-  </si>
-  <si>
-    <t>0.0010,0.5184,0.9967,0.0001</t>
-  </si>
-  <si>
-    <t>0.0288,0.0089,0.9829,0.0002</t>
-  </si>
-  <si>
-    <t>0.7027,0.2638,0.0210,0.0005</t>
-  </si>
-  <si>
-    <t>0.2121,0.9091,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.3365,0.0416,0.7863,0.0059</t>
-  </si>
-  <si>
-    <t>0.8923,0.0051,0.1212,0.0023</t>
-  </si>
-  <si>
-    <t>0.0050,0.0065,0.9923,0.0013</t>
-  </si>
-  <si>
-    <t>0.0688,0.2012,0.9023,0.0003</t>
-  </si>
-  <si>
-    <t>0.6802,0.0304,0.4138,0.0013</t>
-  </si>
-  <si>
-    <t>0.0583,0.5164,0.8931,0.0028</t>
-  </si>
-  <si>
-    <t>0.0199,0.7365,0.8467,0.0002</t>
-  </si>
-  <si>
-    <t>0.9177,0.0011,0.0106,0.0252</t>
-  </si>
-  <si>
-    <t>0.9694,0.0002,0.0008,0.0293</t>
-  </si>
-  <si>
-    <t>0.7575,0.0004,0.0037,0.3550</t>
-  </si>
-  <si>
-    <t>0.8680,0.0008,0.0059,0.1136</t>
-  </si>
-  <si>
-    <t>0.9564,0.0002,0.0049,0.0104</t>
-  </si>
-  <si>
-    <t>0.9785,0.0008,0.0011,0.0084</t>
-  </si>
-  <si>
-    <t>0.0230,0.3795,0.9515,0.0008</t>
-  </si>
-  <si>
-    <t>0.5377,0.0234,0.6511,0.0009</t>
-  </si>
-  <si>
-    <t>0.3518,0.2355,0.5150,0.0043</t>
-  </si>
-  <si>
-    <t>0.2677,0.0049,0.8749,0.0004</t>
-  </si>
-  <si>
-    <t>0.1614,0.1421,0.8283,0.0003</t>
-  </si>
-  <si>
-    <t>0.5516,0.0142,0.6632,0.0005</t>
-  </si>
-  <si>
-    <t>0.9436,0.0052,0.0111,0.0180</t>
-  </si>
-  <si>
-    <t>0.9701,0.0023,0.0031,0.0111</t>
-  </si>
-  <si>
-    <t>0.9366,0.0122,0.0080,0.0138</t>
-  </si>
-  <si>
-    <t>0.9408,0.0034,0.0011,0.0371</t>
-  </si>
-  <si>
-    <t>0.9500,0.0041,0.0027,0.0209</t>
-  </si>
-  <si>
-    <t>0.9629,0.0064,0.0017,0.0080</t>
-  </si>
-  <si>
-    <t>0.9692,0.0012,0.0048,0.0070</t>
-  </si>
-  <si>
-    <t>0.9619,0.0112,0.0031,0.0037</t>
-  </si>
-  <si>
-    <t>0.9454,0.0037,0.0081,0.0224</t>
-  </si>
-  <si>
-    <t>0.9728,0.0017,0.0016,0.0148</t>
-  </si>
-  <si>
-    <t>0.8696,0.0013,0.0019,0.2032</t>
-  </si>
-  <si>
-    <t>0.9749,0.0034,0.0042,0.0062</t>
-  </si>
-  <si>
-    <t>0.9294,0.0016,0.0008,0.0735</t>
-  </si>
-  <si>
-    <t>0.7635,0.0053,0.0085,0.2285</t>
-  </si>
-  <si>
-    <t>0.9502,0.0042,0.0030,0.0143</t>
-  </si>
-  <si>
-    <t>0.9176,0.0067,0.0119,0.0328</t>
-  </si>
-  <si>
-    <t>0.0453,0.0012,0.9850,0.0004</t>
-  </si>
-  <si>
-    <t>0.4606,0.0138,0.6881,0.0005</t>
-  </si>
-  <si>
-    <t>0.9920,0.0002,0.0053,0.0001</t>
-  </si>
-  <si>
-    <t>0.8072,0.0036,0.2946,0.0023</t>
-  </si>
-  <si>
-    <t>0.8025,0.1174,0.0102,0.0037</t>
-  </si>
-  <si>
-    <t>0.8715,0.0638,0.0155,0.0036</t>
-  </si>
-  <si>
-    <t>0.9438,0.0169,0.0110,0.0019</t>
-  </si>
-  <si>
-    <t>0.9310,0.0258,0.0133,0.0021</t>
-  </si>
-  <si>
-    <t>0.8810,0.0597,0.0108,0.0068</t>
-  </si>
-  <si>
-    <t>0.5706,0.3382,0.0553,0.0056</t>
-  </si>
-  <si>
-    <t>0.9312,0.0120,0.0176,0.0055</t>
-  </si>
-  <si>
-    <t>0.9626,0.0036,0.0127,0.0019</t>
-  </si>
-  <si>
-    <t>0.9552,0.0005,0.0392,0.0009</t>
-  </si>
-  <si>
-    <t>0.9751,0.0003,0.0135,0.0005</t>
-  </si>
-  <si>
-    <t>0.9273,0.0024,0.0598,0.0024</t>
-  </si>
-  <si>
-    <t>0.6310,0.0080,0.1663,0.0468</t>
-  </si>
-  <si>
-    <t>0.8780,0.0620,0.0301,0.0011</t>
-  </si>
-  <si>
-    <t>0.9906,0.0011,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.9205,0.0055,0.0566,0.0019</t>
-  </si>
-  <si>
-    <t>0.4932,0.2551,0.1407,0.0008</t>
-  </si>
-  <si>
-    <t>0.8950,0.0333,0.0143,0.0101</t>
-  </si>
-  <si>
-    <t>0.8340,0.0959,0.0553,0.0014</t>
-  </si>
-  <si>
-    <t>0.7235,0.1378,0.0742,0.0075</t>
-  </si>
-  <si>
-    <t>0.9859,0.0019,0.0015,0.0024</t>
-  </si>
-  <si>
-    <t>0.9167,0.0205,0.0179,0.0205</t>
-  </si>
-  <si>
-    <t>0.8948,0.0020,0.0025,0.1416</t>
-  </si>
-  <si>
-    <t>0.9089,0.0066,0.0130,0.0332</t>
-  </si>
-  <si>
-    <t>0.9755,0.0010,0.0027,0.0069</t>
-  </si>
-  <si>
-    <t>0.9871,0.0011,0.0023,0.0011</t>
-  </si>
-  <si>
-    <t>0.7578,0.0367,0.0420,0.0983</t>
-  </si>
-  <si>
-    <t>0.8874,0.0015,0.0053,0.1030</t>
-  </si>
-  <si>
-    <t>0.3188,0.0208,0.8398,0.0008</t>
-  </si>
-  <si>
-    <t>0.3242,0.0427,0.7722,0.0006</t>
-  </si>
-  <si>
-    <t>0.0540,0.0974,0.9618,0.0003</t>
-  </si>
-  <si>
-    <t>0.1378,0.0073,0.9467,0.0001</t>
-  </si>
-  <si>
-    <t>0.9910,0.0002,0.0023,0.0005</t>
-  </si>
-  <si>
-    <t>0.8661,0.0045,0.1607,0.0026</t>
-  </si>
-  <si>
-    <t>0.9231,0.0003,0.0834,0.0012</t>
-  </si>
-  <si>
-    <t>0.9542,0.0017,0.0629,0.0004</t>
-  </si>
-  <si>
-    <t>0.9621,0.0003,0.0056,0.0114</t>
-  </si>
-  <si>
-    <t>0.2644,0.0007,0.0037,0.9027</t>
-  </si>
-  <si>
-    <t>0.9563,0.0003,0.0018,0.0274</t>
-  </si>
-  <si>
-    <t>0.8985,0.0002,0.0065,0.0495</t>
-  </si>
-  <si>
-    <t>0.0149,0.9003,0.7883,0.0016</t>
-  </si>
-  <si>
-    <t>0.8669,0.0067,0.0527,0.0327</t>
-  </si>
-  <si>
-    <t>0.9562,0.0032,0.0072,0.0110</t>
-  </si>
-  <si>
-    <t>0.9170,0.0015,0.0045,0.0623</t>
-  </si>
-  <si>
-    <t>0.9297,0.0121,0.0272,0.0080</t>
-  </si>
-  <si>
-    <t>0.9582,0.0050,0.0195,0.0055</t>
-  </si>
-  <si>
-    <t>0.9727,0.0003,0.0007,0.0180</t>
-  </si>
-  <si>
-    <t>0.9735,0.0009,0.0014,0.0096</t>
-  </si>
-  <si>
-    <t>0.2036,0.0183,0.8750,0.0073</t>
-  </si>
-  <si>
-    <t>0.7818,0.0163,0.0801,0.0681</t>
-  </si>
-  <si>
-    <t>0.9729,0.0018,0.0006,0.0108</t>
-  </si>
-  <si>
-    <t>0.8763,0.0392,0.0187,0.0056</t>
-  </si>
-  <si>
-    <t>0.9914,0.0002,0.0017,0.0012</t>
-  </si>
-  <si>
-    <t>0.9819,0.0015,0.0029,0.0026</t>
-  </si>
-  <si>
-    <t>0.8983,0.0055,0.1840,0.0012</t>
-  </si>
-  <si>
-    <t>0.9735,0.0020,0.0117,0.0006</t>
-  </si>
-  <si>
-    <t>0.9677,0.0026,0.0157,0.0021</t>
-  </si>
-  <si>
-    <t>0.8746,0.0048,0.0043,0.0835</t>
-  </si>
-  <si>
-    <t>0.9559,0.0042,0.0014,0.0209</t>
-  </si>
-  <si>
-    <t>0.9047,0.0062,0.0059,0.0582</t>
-  </si>
-  <si>
-    <t>0.9181,0.0037,0.0088,0.0394</t>
-  </si>
-  <si>
-    <t>0.9359,0.0025,0.0018,0.0537</t>
-  </si>
-  <si>
-    <t>0.6604,0.0637,0.0453,0.0735</t>
-  </si>
-  <si>
-    <t>0.9649,0.0005,0.0014,0.0289</t>
-  </si>
-  <si>
-    <t>0.9135,0.0118,0.0080,0.0276</t>
-  </si>
-  <si>
-    <t>0.9801,0.0016,0.0029,0.0024</t>
-  </si>
-  <si>
-    <t>0.9600,0.0040,0.0076,0.0072</t>
-  </si>
-  <si>
-    <t>0.9404,0.0026,0.0185,0.0092</t>
-  </si>
-  <si>
-    <t>0.8149,0.0912,0.0704,0.0082</t>
-  </si>
-  <si>
-    <t>0.9926,0.0009,0.0002,0.0012</t>
-  </si>
-  <si>
-    <t>0.9332,0.0156,0.0204,0.0090</t>
-  </si>
-  <si>
-    <t>0.9609,0.0007,0.0042,0.0095</t>
-  </si>
-  <si>
-    <t>0.9574,0.0066,0.0071,0.0064</t>
-  </si>
-  <si>
-    <t>0.0051,0.1306,0.9919,0.0016</t>
-  </si>
-  <si>
-    <t>0.9342,0.0012,0.0010,0.0541</t>
-  </si>
-  <si>
-    <t>0.0156,0.0174,0.9932,0.0002</t>
-  </si>
-  <si>
-    <t>0.7767,0.0016,0.5158,0.0002</t>
-  </si>
-  <si>
-    <t>0.9417,0.0011,0.0385,0.0022</t>
-  </si>
-  <si>
-    <t>0.5173,0.0149,0.7059,0.0002</t>
-  </si>
-  <si>
-    <t>0.6923,0.0033,0.5483,0.0004</t>
-  </si>
-  <si>
-    <t>0.0850,0.0017,0.9651,0.0003</t>
-  </si>
-  <si>
-    <t>0.0708,0.0109,0.9406,0.0011</t>
-  </si>
-  <si>
-    <t>0.9843,0.0003,0.0098,0.0005</t>
-  </si>
-  <si>
-    <t>0.9689,0.0008,0.0224,0.0008</t>
-  </si>
-  <si>
-    <t>0.9297,0.0031,0.0513,0.0016</t>
-  </si>
-  <si>
-    <t>0.8073,0.0123,0.1851,0.0066</t>
-  </si>
-  <si>
-    <t>0.9734,0.0020,0.0179,0.0007</t>
-  </si>
-  <si>
-    <t>0.9898,0.0003,0.0077,0.0002</t>
-  </si>
-  <si>
-    <t>0.9750,0.0011,0.0177,0.0008</t>
-  </si>
-  <si>
-    <t>0.9825,0.0003,0.0067,0.0005</t>
-  </si>
-  <si>
-    <t>0.8168,0.0699,0.0148,0.0217</t>
-  </si>
-  <si>
-    <t>0.8989,0.0729,0.0022,0.0013</t>
-  </si>
-  <si>
-    <t>0.9613,0.0080,0.0029,0.0039</t>
-  </si>
-  <si>
-    <t>0.9763,0.0015,0.0014,0.0092</t>
-  </si>
-  <si>
-    <t>0.9556,0.0131,0.0043,0.0060</t>
-  </si>
-  <si>
-    <t>0.9725,0.0027,0.0170,0.0004</t>
-  </si>
-  <si>
-    <t>0.9622,0.0003,0.0235,0.0011</t>
-  </si>
-  <si>
-    <t>0.9213,0.0007,0.0487,0.0036</t>
-  </si>
-  <si>
-    <t>0.9554,0.0011,0.0463,0.0010</t>
-  </si>
-  <si>
-    <t>0.9418,0.0004,0.0413,0.0019</t>
-  </si>
-  <si>
-    <t>0.0952,0.0299,0.9390,0.0024</t>
-  </si>
-  <si>
-    <t>0.1586,0.0069,0.8348,0.0053</t>
-  </si>
-  <si>
-    <t>0.5838,0.0017,0.7359,0.0001</t>
-  </si>
-  <si>
-    <t>0.2420,0.0067,0.8981,0.0004</t>
-  </si>
-  <si>
-    <t>0.4398,0.0079,0.7953,0.0003</t>
-  </si>
-  <si>
-    <t>0.9252,0.0005,0.0004,0.1155</t>
-  </si>
-  <si>
-    <t>0.9356,0.0015,0.0014,0.0583</t>
-  </si>
-  <si>
-    <t>0.9313,0.0047,0.0026,0.0281</t>
-  </si>
-  <si>
-    <t>0.8343,0.0117,0.0050,0.0939</t>
-  </si>
-  <si>
-    <t>0.8802,0.0163,0.0109,0.0503</t>
-  </si>
-  <si>
-    <t>0.8832,0.0109,0.0057,0.0471</t>
-  </si>
-  <si>
-    <t>0.9420,0.0016,0.0015,0.0444</t>
-  </si>
-  <si>
-    <t>0.9637,0.0049,0.0040,0.0076</t>
-  </si>
-  <si>
-    <t>0.3827,0.0127,0.7447,0.0053</t>
-  </si>
-  <si>
-    <t>0.9268,0.0015,0.0133,0.0178</t>
-  </si>
-  <si>
-    <t>0.8768,0.0063,0.0346,0.0306</t>
-  </si>
-  <si>
-    <t>0.0301,0.0535,0.9757,0.0005</t>
-  </si>
-  <si>
-    <t>0.0742,0.0633,0.9055,0.0014</t>
-  </si>
-  <si>
-    <t>0.7814,0.0176,0.2416,0.0039</t>
-  </si>
-  <si>
-    <t>0.0195,0.0110,0.9934,0.0001</t>
-  </si>
-  <si>
-    <t>0.9315,0.0019,0.1501,0.0003</t>
-  </si>
-  <si>
-    <t>0.0174,0.0025,0.9929,0.0001</t>
-  </si>
-  <si>
-    <t>0.5879,0.0321,0.4884,0.0026</t>
-  </si>
-  <si>
-    <t>0.8733,0.0093,0.1386,0.0029</t>
-  </si>
-  <si>
-    <t>0.9846,0.0001,0.0217,0.0002</t>
-  </si>
-  <si>
-    <t>0.9509,0.0010,0.0510,0.0010</t>
-  </si>
-  <si>
-    <t>0.9887,0.0001,0.0031,0.0007</t>
-  </si>
-  <si>
-    <t>0.9865,0.0012,0.0018,0.0044</t>
-  </si>
-  <si>
-    <t>0.8832,0.0239,0.0123,0.0173</t>
-  </si>
-  <si>
-    <t>0.8633,0.0022,0.0068,0.1000</t>
-  </si>
-  <si>
-    <t>0.9731,0.0048,0.0026,0.0032</t>
-  </si>
-  <si>
-    <t>0.9375,0.0035,0.0011,0.0238</t>
-  </si>
-  <si>
-    <t>0.8899,0.0091,0.0054,0.0466</t>
-  </si>
-  <si>
-    <t>0.9200,0.0086,0.0161,0.0362</t>
-  </si>
-  <si>
-    <t>0.9790,0.0020,0.0015,0.0063</t>
-  </si>
-  <si>
-    <t>0.7021,0.0116,0.4080,0.0026</t>
-  </si>
-  <si>
-    <t>0.5300,0.0215,0.5982,0.0040</t>
-  </si>
-  <si>
-    <t>0.2166,0.0072,0.9176,0.0004</t>
-  </si>
-  <si>
-    <t>0.9056,0.0052,0.1005,0.0015</t>
-  </si>
-  <si>
-    <t>0.0188,0.0066,0.9877,0.0002</t>
-  </si>
-  <si>
-    <t>0.9091,0.0012,0.0834,0.0045</t>
-  </si>
-  <si>
-    <t>0.9947,0.0002,0.0025,0.0000</t>
-  </si>
-  <si>
-    <t>0.5233,0.0049,0.4968,0.0063</t>
-  </si>
-  <si>
-    <t>0.9755,0.0007,0.0029,0.0067</t>
-  </si>
-  <si>
-    <t>0.9366,0.0017,0.0265,0.0051</t>
-  </si>
-  <si>
-    <t>0.9247,0.0003,0.0019,0.0652</t>
-  </si>
-  <si>
-    <t>0.8101,0.0000,0.0004,0.3642</t>
-  </si>
-  <si>
-    <t>0.8974,0.0001,0.0005,0.1602</t>
-  </si>
-  <si>
-    <t>0.9274,0.0036,0.0475,0.0046</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0.7835,0.0098,0.0228,0.1770</t>
+  </si>
+  <si>
+    <t>0.0554,0.0089,0.0023,0.9673</t>
+  </si>
+  <si>
+    <t>0.9448,0.0041,0.0024,0.0528</t>
+  </si>
+  <si>
+    <t>0.4481,0.0023,0.0002,0.7465</t>
+  </si>
+  <si>
+    <t>0.9974,0.0006,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9961,0.0036,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9934,0.0038,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9974,0.0007,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9906,0.0089,0.0012,0.0008</t>
+  </si>
+  <si>
+    <t>0.9965,0.0022,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9980,0.0005,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9913,0.0037,0.0032,0.0011</t>
+  </si>
+  <si>
+    <t>0.9599,0.0031,0.0467,0.0009</t>
+  </si>
+  <si>
+    <t>0.0135,0.0027,0.9885,0.0009</t>
+  </si>
+  <si>
+    <t>0.9562,0.0007,0.1032,0.0002</t>
+  </si>
+  <si>
+    <t>0.1555,0.0049,0.9075,0.0003</t>
+  </si>
+  <si>
+    <t>0.9199,0.0070,0.1099,0.0016</t>
+  </si>
+  <si>
+    <t>0.0002,0.9989,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.9979,0.0008,0.0015</t>
+  </si>
+  <si>
+    <t>0.1715,0.8838,0.0071,0.0014</t>
+  </si>
+  <si>
+    <t>0.0024,0.9925,0.0035,0.0028</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.8097,0.0093,0.2494,0.0031</t>
+  </si>
+  <si>
+    <t>0.4903,0.0074,0.5567,0.0061</t>
+  </si>
+  <si>
+    <t>0.0053,0.0016,0.9937,0.0004</t>
+  </si>
+  <si>
+    <t>0.0232,0.0014,0.9652,0.0067</t>
+  </si>
+  <si>
+    <t>0.0183,0.0147,0.9782,0.0017</t>
+  </si>
+  <si>
+    <t>0.0028,0.0003,0.9970,0.0002</t>
+  </si>
+  <si>
+    <t>0.0083,0.0018,0.9909,0.0009</t>
+  </si>
+  <si>
+    <t>0.0811,0.8862,0.0384,0.0006</t>
+  </si>
+  <si>
+    <t>0.3043,0.5552,0.1372,0.0023</t>
+  </si>
+  <si>
+    <t>0.0020,0.0123,0.9967,0.0023</t>
+  </si>
+  <si>
+    <t>0.0051,0.9747,0.0124,0.0002</t>
+  </si>
+  <si>
+    <t>0.7949,0.1615,0.0751,0.0138</t>
+  </si>
+  <si>
+    <t>0.0426,0.0226,0.9530,0.0195</t>
+  </si>
+  <si>
+    <t>0.0863,0.9389,0.0027,0.0010</t>
+  </si>
+  <si>
+    <t>0.0040,0.9909,0.0692,0.0015</t>
+  </si>
+  <si>
+    <t>0.0123,0.8966,0.0488,0.0229</t>
+  </si>
+  <si>
+    <t>0.0261,0.0030,0.9735,0.0018</t>
+  </si>
+  <si>
+    <t>0.3285,0.0045,0.8063,0.0009</t>
+  </si>
+  <si>
+    <t>0.0393,0.0051,0.9003,0.0533</t>
+  </si>
+  <si>
+    <t>0.0112,0.0937,0.9744,0.0015</t>
+  </si>
+  <si>
+    <t>0.0066,0.9680,0.0132,0.0001</t>
+  </si>
+  <si>
+    <t>0.0062,0.0024,0.9902,0.0004</t>
+  </si>
+  <si>
+    <t>0.0030,0.9024,0.0016,0.6422</t>
+  </si>
+  <si>
+    <t>0.0016,0.9906,0.0125,0.0042</t>
+  </si>
+  <si>
+    <t>0.0022,0.9938,0.0051,0.0011</t>
+  </si>
+  <si>
+    <t>0.0019,0.9949,0.0318,0.0008</t>
+  </si>
+  <si>
+    <t>0.0039,0.0350,0.9755,0.0037</t>
+  </si>
+  <si>
+    <t>0.0037,0.0950,0.9916,0.0005</t>
+  </si>
+  <si>
+    <t>0.0095,0.0036,0.9835,0.0014</t>
+  </si>
+  <si>
+    <t>0.0209,0.0004,0.9885,0.0003</t>
+  </si>
+  <si>
+    <t>0.0197,0.0096,0.9711,0.0021</t>
+  </si>
+  <si>
+    <t>0.0037,0.0262,0.9839,0.0026</t>
+  </si>
+  <si>
+    <t>0.9842,0.0173,0.0014,0.0005</t>
+  </si>
+  <si>
+    <t>0.9736,0.0120,0.0111,0.0016</t>
+  </si>
+  <si>
+    <t>0.9951,0.0067,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0028,0.0239,0.9918,0.0102</t>
+  </si>
+  <si>
+    <t>0.9800,0.0083,0.0084,0.0025</t>
+  </si>
+  <si>
+    <t>0.9941,0.0055,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9950,0.0042,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0008,0.9811,0.9564,0.0006</t>
+  </si>
+  <si>
+    <t>0.0222,0.0362,0.9660,0.0024</t>
+  </si>
+  <si>
+    <t>0.0135,0.0553,0.9776,0.0022</t>
+  </si>
+  <si>
+    <t>0.0004,0.9798,0.9706,0.0003</t>
+  </si>
+  <si>
+    <t>0.0010,0.0013,0.9973,0.0005</t>
+  </si>
+  <si>
+    <t>0.0027,0.9952,0.0035,0.0003</t>
+  </si>
+  <si>
+    <t>0.0017,0.9970,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.5736,0.0157,0.5457,0.0113</t>
+  </si>
+  <si>
+    <t>0.8900,0.0092,0.1921,0.0019</t>
+  </si>
+  <si>
+    <t>0.0044,0.0032,0.9930,0.0013</t>
+  </si>
+  <si>
+    <t>0.0003,0.9736,0.9806,0.0002</t>
+  </si>
+  <si>
+    <t>0.0072,0.6494,0.9131,0.0009</t>
+  </si>
+  <si>
+    <t>0.0049,0.9856,0.0135,0.0008</t>
+  </si>
+  <si>
+    <t>0.0024,0.9787,0.5018,0.0004</t>
+  </si>
+  <si>
+    <t>0.1166,0.0008,0.0186,0.8938</t>
+  </si>
+  <si>
+    <t>0.0017,0.0014,0.0001,0.9989</t>
+  </si>
+  <si>
+    <t>0.0035,0.0024,0.0003,0.9978</t>
+  </si>
+  <si>
+    <t>0.0296,0.0070,0.0052,0.9793</t>
+  </si>
+  <si>
+    <t>0.0166,0.0011,0.0014,0.9934</t>
+  </si>
+  <si>
+    <t>0.0019,0.0148,0.0013,0.9968</t>
+  </si>
+  <si>
+    <t>0.0002,0.9698,0.9906,0.0002</t>
+  </si>
+  <si>
+    <t>0.0115,0.6419,0.9216,0.0019</t>
+  </si>
+  <si>
+    <t>0.0411,0.6520,0.4012,0.0008</t>
+  </si>
+  <si>
+    <t>0.0008,0.9729,0.7361,0.0004</t>
+  </si>
+  <si>
+    <t>0.0025,0.9691,0.5918,0.0008</t>
+  </si>
+  <si>
+    <t>0.0038,0.9377,0.6419,0.0013</t>
+  </si>
+  <si>
+    <t>0.9961,0.0035,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9619,0.0266,0.0122,0.0019</t>
+  </si>
+  <si>
+    <t>0.9920,0.0051,0.0014,0.0006</t>
+  </si>
+  <si>
+    <t>0.9950,0.0015,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.9885,0.0128,0.0009,0.0007</t>
+  </si>
+  <si>
+    <t>0.9980,0.0004,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9853,0.0051,0.0064,0.0021</t>
+  </si>
+  <si>
+    <t>0.9941,0.0047,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9964,0.0013,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9972,0.0006,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9969,0.0003,0.0001,0.0014</t>
+  </si>
+  <si>
+    <t>0.9894,0.0035,0.0060,0.0005</t>
+  </si>
+  <si>
+    <t>0.9944,0.0019,0.0027,0.0004</t>
+  </si>
+  <si>
+    <t>0.9956,0.0010,0.0006,0.0015</t>
+  </si>
+  <si>
+    <t>0.0836,0.0015,0.9740,0.0002</t>
+  </si>
+  <si>
+    <t>0.5566,0.0015,0.6381,0.0007</t>
+  </si>
+  <si>
+    <t>0.9783,0.0025,0.0067,0.0013</t>
+  </si>
+  <si>
+    <t>0.0033,0.0016,0.9946,0.0016</t>
+  </si>
+  <si>
+    <t>0.0160,0.9773,0.0019,0.0020</t>
+  </si>
+  <si>
+    <t>0.0019,0.9961,0.0033,0.0003</t>
+  </si>
+  <si>
+    <t>0.4841,0.5532,0.0068,0.0105</t>
+  </si>
+  <si>
+    <t>0.0064,0.9900,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.0051,0.9922,0.0032,0.0004</t>
+  </si>
+  <si>
+    <t>0.0030,0.9929,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.9554,0.0440,0.0039,0.0007</t>
+  </si>
+  <si>
+    <t>0.9285,0.0128,0.0512,0.0044</t>
+  </si>
+  <si>
+    <t>0.4807,0.0058,0.6397,0.0032</t>
+  </si>
+  <si>
+    <t>0.8481,0.0120,0.1883,0.0052</t>
+  </si>
+  <si>
+    <t>0.6612,0.0322,0.3756,0.0038</t>
+  </si>
+  <si>
+    <t>0.0275,0.0977,0.0786,0.8846</t>
+  </si>
+  <si>
+    <t>0.0024,0.9907,0.0061,0.0028</t>
+  </si>
+  <si>
+    <t>0.0016,0.9929,0.0026,0.0064</t>
+  </si>
+  <si>
+    <t>0.0005,0.9957,0.0037,0.0022</t>
+  </si>
+  <si>
+    <t>0.0003,0.9961,0.3875,0.0009</t>
+  </si>
+  <si>
+    <t>0.0009,0.9967,0.0027,0.0005</t>
+  </si>
+  <si>
+    <t>0.8764,0.1534,0.0085,0.0010</t>
+  </si>
+  <si>
+    <t>0.6517,0.3938,0.0161,0.0022</t>
+  </si>
+  <si>
+    <t>0.9953,0.0021,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9937,0.0023,0.0006,0.0017</t>
+  </si>
+  <si>
+    <t>0.9795,0.0099,0.0086,0.0019</t>
+  </si>
+  <si>
+    <t>0.9400,0.0392,0.0257,0.0022</t>
+  </si>
+  <si>
+    <t>0.9985,0.0001,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9579,0.0133,0.0238,0.0011</t>
+  </si>
+  <si>
+    <t>0.9920,0.0025,0.0009,0.0014</t>
+  </si>
+  <si>
+    <t>0.9944,0.0009,0.0013,0.0008</t>
+  </si>
+  <si>
+    <t>0.0006,0.8952,0.9813,0.0004</t>
+  </si>
+  <si>
+    <t>0.0120,0.4434,0.9130,0.0006</t>
+  </si>
+  <si>
+    <t>0.0146,0.0233,0.9762,0.0023</t>
+  </si>
+  <si>
+    <t>0.0309,0.0816,0.9284,0.0017</t>
+  </si>
+  <si>
+    <t>0.9882,0.0051,0.0018,0.0004</t>
+  </si>
+  <si>
+    <t>0.3743,0.0109,0.7414,0.0046</t>
+  </si>
+  <si>
+    <t>0.0828,0.0014,0.9514,0.0022</t>
+  </si>
+  <si>
+    <t>0.9179,0.0146,0.0465,0.0041</t>
+  </si>
+  <si>
+    <t>0.3642,0.0034,0.0014,0.8324</t>
+  </si>
+  <si>
+    <t>0.0002,0.0044,0.0001,0.9996</t>
+  </si>
+  <si>
+    <t>0.0009,0.0244,0.0005,0.9974</t>
+  </si>
+  <si>
+    <t>0.0555,0.0005,0.0015,0.9848</t>
+  </si>
+  <si>
+    <t>0.0013,0.9849,0.2647,0.0011</t>
+  </si>
+  <si>
+    <t>0.9935,0.0040,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.0221,0.9595,0.0091,0.0043</t>
+  </si>
+  <si>
+    <t>0.9778,0.0083,0.0039,0.0060</t>
+  </si>
+  <si>
+    <t>0.1991,0.8187,0.0090,0.0017</t>
+  </si>
+  <si>
+    <t>0.9725,0.0108,0.0094,0.0044</t>
+  </si>
+  <si>
+    <t>0.8374,0.0158,0.0049,0.1340</t>
+  </si>
+  <si>
+    <t>0.9896,0.0048,0.0028,0.0012</t>
+  </si>
+  <si>
+    <t>0.0075,0.1101,0.9776,0.0184</t>
+  </si>
+  <si>
+    <t>0.6322,0.0033,0.0077,0.4613</t>
+  </si>
+  <si>
+    <t>0.9729,0.0079,0.0015,0.0119</t>
+  </si>
+  <si>
+    <t>0.8617,0.0736,0.0455,0.0037</t>
+  </si>
+  <si>
+    <t>0.9866,0.0042,0.0018,0.0016</t>
+  </si>
+  <si>
+    <t>0.6830,0.1708,0.0540,0.0216</t>
+  </si>
+  <si>
+    <t>0.1035,0.8872,0.0366,0.0101</t>
+  </si>
+  <si>
+    <t>0.4055,0.5030,0.0370,0.0022</t>
+  </si>
+  <si>
+    <t>0.9181,0.0467,0.0311,0.0029</t>
+  </si>
+  <si>
+    <t>0.9848,0.0079,0.0042,0.0017</t>
+  </si>
+  <si>
+    <t>0.9826,0.0093,0.0080,0.0006</t>
+  </si>
+  <si>
+    <t>0.9865,0.0011,0.0052,0.0022</t>
+  </si>
+  <si>
+    <t>0.9921,0.0013,0.0036,0.0012</t>
+  </si>
+  <si>
+    <t>0.9894,0.0023,0.0022,0.0026</t>
+  </si>
+  <si>
+    <t>0.9708,0.0126,0.0154,0.0007</t>
+  </si>
+  <si>
+    <t>0.9947,0.0010,0.0015,0.0006</t>
+  </si>
+  <si>
+    <t>0.9944,0.0007,0.0022,0.0007</t>
+  </si>
+  <si>
+    <t>0.8083,0.1529,0.0031,0.0218</t>
+  </si>
+  <si>
+    <t>0.9495,0.0872,0.0027,0.0004</t>
+  </si>
+  <si>
+    <t>0.5173,0.6166,0.0038,0.0014</t>
+  </si>
+  <si>
+    <t>0.7857,0.1954,0.0484,0.0090</t>
+  </si>
+  <si>
+    <t>0.9870,0.0111,0.0018,0.0010</t>
+  </si>
+  <si>
+    <t>0.9649,0.0272,0.0027,0.0042</t>
+  </si>
+  <si>
+    <t>0.9796,0.0118,0.0077,0.0003</t>
+  </si>
+  <si>
+    <t>0.9457,0.0565,0.0043,0.0023</t>
+  </si>
+  <si>
+    <t>0.0053,0.0224,0.9949,0.0010</t>
+  </si>
+  <si>
+    <t>0.9519,0.0304,0.0133,0.0029</t>
+  </si>
+  <si>
+    <t>0.0016,0.0034,0.9975,0.0002</t>
+  </si>
+  <si>
+    <t>0.0128,0.0224,0.9809,0.0011</t>
+  </si>
+  <si>
+    <t>0.0048,0.0095,0.9919,0.0010</t>
+  </si>
+  <si>
+    <t>0.0093,0.0498,0.9651,0.0006</t>
+  </si>
+  <si>
+    <t>0.0011,0.0023,0.9978,0.0002</t>
+  </si>
+  <si>
+    <t>0.0047,0.0006,0.9948,0.0005</t>
+  </si>
+  <si>
+    <t>0.0064,0.0013,0.9900,0.0008</t>
+  </si>
+  <si>
+    <t>0.1133,0.0307,0.8652,0.0111</t>
+  </si>
+  <si>
+    <t>0.0316,0.0077,0.9640,0.0037</t>
+  </si>
+  <si>
+    <t>0.4670,0.0081,0.7247,0.0033</t>
+  </si>
+  <si>
+    <t>0.0834,0.7693,0.1657,0.0076</t>
+  </si>
+  <si>
+    <t>0.2144,0.1471,0.7447,0.0023</t>
+  </si>
+  <si>
+    <t>0.0567,0.0198,0.9148,0.0078</t>
+  </si>
+  <si>
+    <t>0.5087,0.0162,0.5144,0.0218</t>
+  </si>
+  <si>
+    <t>0.8124,0.0279,0.2181,0.0023</t>
+  </si>
+  <si>
+    <t>0.2413,0.8485,0.0035,0.0010</t>
+  </si>
+  <si>
+    <t>0.3456,0.7598,0.0033,0.0023</t>
+  </si>
+  <si>
+    <t>0.9425,0.0840,0.0013,0.0017</t>
+  </si>
+  <si>
+    <t>0.9609,0.0573,0.0022,0.0006</t>
+  </si>
+  <si>
+    <t>0.6151,0.6524,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9342,0.0331,0.0142,0.0054</t>
+  </si>
+  <si>
+    <t>0.9604,0.0026,0.0375,0.0017</t>
+  </si>
+  <si>
+    <t>0.9576,0.0005,0.0349,0.0016</t>
+  </si>
+  <si>
+    <t>0.9333,0.0021,0.0516,0.0035</t>
+  </si>
+  <si>
+    <t>0.6623,0.0042,0.4766,0.0054</t>
+  </si>
+  <si>
+    <t>0.0214,0.0115,0.9661,0.0180</t>
+  </si>
+  <si>
+    <t>0.0030,0.0282,0.9896,0.0037</t>
+  </si>
+  <si>
+    <t>0.0072,0.0118,0.9871,0.0026</t>
+  </si>
+  <si>
+    <t>0.0196,0.0216,0.9667,0.0017</t>
+  </si>
+  <si>
+    <t>0.0031,0.0097,0.9787,0.0013</t>
+  </si>
+  <si>
+    <t>0.9955,0.0023,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9854,0.0070,0.0042,0.0014</t>
+  </si>
+  <si>
+    <t>0.9809,0.0236,0.0021,0.0008</t>
+  </si>
+  <si>
+    <t>0.9906,0.0093,0.0016,0.0005</t>
+  </si>
+  <si>
+    <t>0.9542,0.0255,0.0069,0.0121</t>
+  </si>
+  <si>
+    <t>0.9889,0.0053,0.0037,0.0007</t>
+  </si>
+  <si>
+    <t>0.9926,0.0043,0.0014,0.0008</t>
+  </si>
+  <si>
+    <t>0.9931,0.0029,0.0008,0.0018</t>
+  </si>
+  <si>
+    <t>0.0849,0.0769,0.8996,0.0233</t>
+  </si>
+  <si>
+    <t>0.0531,0.7839,0.1655,0.0447</t>
+  </si>
+  <si>
+    <t>0.6194,0.0271,0.2016,0.0482</t>
+  </si>
+  <si>
+    <t>0.0032,0.0035,0.9931,0.0016</t>
+  </si>
+  <si>
+    <t>0.0012,0.0006,0.9964,0.0006</t>
+  </si>
+  <si>
+    <t>0.0040,0.0167,0.9779,0.0007</t>
+  </si>
+  <si>
+    <t>0.0049,0.0018,0.9961,0.0001</t>
+  </si>
+  <si>
+    <t>0.0699,0.0033,0.9263,0.0011</t>
+  </si>
+  <si>
+    <t>0.0017,0.0022,0.9969,0.0009</t>
+  </si>
+  <si>
+    <t>0.0081,0.0024,0.9925,0.0005</t>
+  </si>
+  <si>
+    <t>0.0109,0.0249,0.9643,0.0095</t>
+  </si>
+  <si>
+    <t>0.9136,0.0004,0.1873,0.0004</t>
+  </si>
+  <si>
+    <t>0.2805,0.0017,0.8562,0.0013</t>
+  </si>
+  <si>
+    <t>0.9439,0.0003,0.0869,0.0006</t>
+  </si>
+  <si>
+    <t>0.9880,0.0053,0.0044,0.0010</t>
+  </si>
+  <si>
+    <t>0.9956,0.0026,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9977,0.0014,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9965,0.0018,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9958,0.0017,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9944,0.0042,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.9969,0.0015,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9969,0.0026,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0986,0.0932,0.7293,0.0015</t>
+  </si>
+  <si>
+    <t>0.0026,0.3464,0.9805,0.0019</t>
+  </si>
+  <si>
+    <t>0.0132,0.0166,0.9825,0.0016</t>
+  </si>
+  <si>
+    <t>0.0486,0.0210,0.9413,0.0031</t>
+  </si>
+  <si>
+    <t>0.0010,0.0012,0.9966,0.0005</t>
+  </si>
+  <si>
+    <t>0.0290,0.0035,0.7475,0.3388</t>
+  </si>
+  <si>
+    <t>0.1998,0.0261,0.8498,0.0097</t>
+  </si>
+  <si>
+    <t>0.0746,0.0120,0.7269,0.0579</t>
+  </si>
+  <si>
+    <t>0.8849,0.0029,0.0089,0.0930</t>
+  </si>
+  <si>
+    <t>0.0038,0.0771,0.0014,0.9914</t>
+  </si>
+  <si>
+    <t>0.1247,0.0043,0.0005,0.9546</t>
+  </si>
+  <si>
+    <t>0.0038,0.0003,0.0006,0.9982</t>
+  </si>
+  <si>
+    <t>0.0022,0.0002,0.0001,0.9991</t>
+  </si>
+  <si>
+    <t>0.9049,0.0034,0.0003,0.0955</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,10 +1970,10 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,10 +1998,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2057,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2071,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2085,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2113,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2127,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2141,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2155,7 @@
         <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2169,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2183,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2191,10 +2194,10 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2205,10 +2208,10 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2222,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2233,10 +2236,10 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2247,10 +2250,10 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2267,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2278,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2295,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,10 +2306,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,10 +2320,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2337,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2351,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2362,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2376,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2393,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2404,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2421,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2432,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2446,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,10 +2460,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2474,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2491,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,10 +2502,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2519,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2533,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2547,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2561,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2572,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2583,10 +2586,10 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2597,10 +2600,10 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2611,10 +2614,10 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2631,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2645,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2659,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2667,10 +2670,10 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2687,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2701,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2729,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2743,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2757,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2771,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2785,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2799,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2813,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2821,10 +2824,10 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2841,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2855,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2869,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2877,10 +2880,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2911,7 @@
         <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2925,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2939,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,10 +2950,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2964,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,10 +2978,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +2995,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,10 +3006,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,10 +3020,10 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,10 +3034,10 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,10 +3048,10 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,10 +3062,10 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,10 +3076,10 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,10 +3090,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3104,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3118,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3132,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,10 +3146,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,10 +3160,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3317,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3359,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3373,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3387,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3401,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3415,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3429,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,10 +3440,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3451,10 +3454,10 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3465,10 +3468,10 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3479,10 +3482,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,10 +3496,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3507,10 +3510,10 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3521,10 +3524,10 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3541,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3555,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3566,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3583,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3597,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3608,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3619,10 +3622,10 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3633,10 +3636,10 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,10 +3650,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,10 +3664,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,10 +3678,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3695,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3709,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3751,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3779,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3793,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3832,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3849,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3863,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3877,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3891,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,10 +3902,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3916,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,10 +3944,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3961,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,10 +3972,10 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,10 +3986,10 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4000,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4028,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4056,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4073,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4115,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4157,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4196,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,10 +4210,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4311,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4353,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4367,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4378,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4395,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4409,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4423,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4437,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4451,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4479,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4507,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,10 +4518,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4535,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4549,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4563,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4577,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4588,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4602,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4616,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4630,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4644,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4658,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4672,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4689,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4700,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4714,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4731,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4745,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4756,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4773,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4787,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4801,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4815,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4843,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4857,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4871,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4885,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4899,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4941,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4955,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4983,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +4997,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5011,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5025,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5036,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5053,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,10 +5092,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5109,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,10 +5120,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5137,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5145,10 +5148,10 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5162,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5190,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5249,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5263,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5277,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5291,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5305,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5330,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5347,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5361,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5372,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5389,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5400,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5414,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5428,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5445,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,10 +5456,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,10 +5470,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,10 +5484,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,10 +5498,10 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5515,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
